--- a/www/download/IND.surplus_value.empe.r.pc.rpPE.xlsx
+++ b/www/download/IND.surplus_value.empe.r.pc.rpPE.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Petrovic</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-46.83</t>
+          <t>-0.468335558077739</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-50.95</t>
+          <t>-0.509546548569383</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-50.54</t>
+          <t>-0.505417152489045</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-43.21</t>
+          <t>-0.43205257950582</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-43.86</t>
+          <t>-0.438643999073211</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-39.54</t>
+          <t>-0.395404749458206</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-35.9</t>
+          <t>-0.358988204831643</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-38.35</t>
+          <t>-0.3834895897025</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>-47</t>
+          <t>-0.469994176866503</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-51.52</t>
+          <t>-0.515200266913774</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>-52.54</t>
+          <t>-0.525433320573028</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>-52.82</t>
+          <t>-0.528202792928823</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-55.02</t>
+          <t>-0.550176620030907</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-52.35</t>
+          <t>-0.523490946376089</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-50.77</t>
+          <t>-0.507674440079808</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-64.53</t>
+          <t>-0.645268721595561</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-62.34</t>
+          <t>-0.623405541039749</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-57.22</t>
+          <t>-0.572197467484289</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-57.77</t>
+          <t>-0.577729774837484</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-54.34</t>
+          <t>-0.543442671077404</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-48.33</t>
+          <t>-0.483251455023673</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-48.03</t>
+          <t>-0.480320005966654</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-50.87</t>
+          <t>-0.508683330669312</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-57.57</t>
+          <t>-0.575734777408162</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-56.88</t>
+          <t>-0.568753696794486</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>-56.4</t>
+          <t>-0.563957912470022</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>-56.68</t>
+          <t>-0.566846181758669</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>-57.25</t>
+          <t>-0.572482480788843</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>-58.24</t>
+          <t>-0.582384995329974</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>-58.54</t>
+          <t>-0.585418162685976</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-73.36</t>
+          <t>-0.733550822127886</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-71.67</t>
+          <t>-0.716714801730766</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-68.37</t>
+          <t>-0.683739629648212</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-68.46</t>
+          <t>-0.684588404659595</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-66.71</t>
+          <t>-0.667063645859151</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-61.76</t>
+          <t>-0.617578750197713</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-62.49</t>
+          <t>-0.624885835917966</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-65.06</t>
+          <t>-0.650560829382938</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-69.62</t>
+          <t>-0.696165922766683</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-69.71</t>
+          <t>-0.697125968566822</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-68.51</t>
+          <t>-0.685127540637877</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>-68.09</t>
+          <t>-0.68085499481551</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>-68.23</t>
+          <t>-0.68226330268733</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>-67.88</t>
+          <t>-0.678794526509332</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>-68.19</t>
+          <t>-0.681860072928255</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>408.28</t>
+          <t>4.08276173009445</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>481.16</t>
+          <t>4.81162882719268</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>600.41</t>
+          <t>6.00405856223451</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>369.68</t>
+          <t>3.69680497967126</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>391.94</t>
+          <t>3.91941802831353</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>400.38</t>
+          <t>4.00375927410349</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>346.8</t>
+          <t>3.46795764622235</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>306.41</t>
+          <t>3.06409543535342</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>264.06</t>
+          <t>2.64057216887019</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>255.56</t>
+          <t>2.55562214220573</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>2.54100407221736</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>249.58</t>
+          <t>2.49578891570569</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>216.03</t>
+          <t>2.16028829966212</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>178.54</t>
+          <t>1.78539928915645</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>163.04</t>
+          <t>1.6304256302835</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>125.91</t>
+          <t>1.25911914835268</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>111.04</t>
+          <t>1.11044745214861</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>112.29</t>
+          <t>1.12291269592755</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>1.13003201431733</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>234.7</t>
+          <t>2.34701975577027</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>226.94</t>
+          <t>2.26936286944756</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>279.83</t>
+          <t>2.79825542240484</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>343.69</t>
+          <t>3.43687462729449</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>366.89</t>
+          <t>3.66888773215208</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>349.7</t>
+          <t>3.49701837102455</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>262.86</t>
+          <t>2.62860494159664</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>222.24</t>
+          <t>2.22235527945147</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>200.7</t>
+          <t>2.00698249142108</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>178.43</t>
+          <t>1.78429956966314</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>168.43</t>
+          <t>1.684251798011</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-22.27</t>
+          <t>-0.222680331867563</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-22.61</t>
+          <t>-0.226134718118933</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-25.99</t>
+          <t>-0.25989404489102</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-23.4</t>
+          <t>-0.233959166013446</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-22.24</t>
+          <t>-0.222383511282317</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-26.19</t>
+          <t>-0.261856822543782</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-26.78</t>
+          <t>-0.267836226571497</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-26.47</t>
+          <t>-0.264696961870489</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>-33.15</t>
+          <t>-0.331450683152824</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-33.96</t>
+          <t>-0.339566632336551</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>-37.53</t>
+          <t>-0.375339342783715</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>-41.36</t>
+          <t>-0.413566207161931</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>-39.81</t>
+          <t>-0.398144606539211</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>-38.13</t>
+          <t>-0.381330304083512</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>-34.95</t>
+          <t>-0.349486960419669</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>446.94</t>
+          <t>4.46943921595488</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>398.33</t>
+          <t>3.98326029167706</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>360.39</t>
+          <t>3.60393437086935</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>338.27</t>
+          <t>3.38269843214542</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>346.12</t>
+          <t>3.46115953659216</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>328.43</t>
+          <t>3.28426237154231</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>330.43</t>
+          <t>3.3042597439661</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>343.83</t>
+          <t>3.43832508583927</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>362.68</t>
+          <t>3.62684344857361</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>350.56</t>
+          <t>3.50556698920028</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>342.71</t>
+          <t>3.42714667470216</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>310.9</t>
+          <t>3.10901931130449</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>287.9</t>
+          <t>2.87899935453522</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>247.62</t>
+          <t>2.47616584539107</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>214.25</t>
+          <t>2.14251382131655</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>5.89</t>
+          <t>0.0588801643209682</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>0.07378336039471</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>0.0741482408019929</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.00619927864842973</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>6.43</t>
+          <t>0.0642599005611448</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>16.4</t>
+          <t>0.164023774584693</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>15.23</t>
+          <t>0.152305936146141</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>0.0659920845788287</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>-11.86</t>
+          <t>-0.118622969213534</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-17.38</t>
+          <t>-0.173785927062979</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>-16.91</t>
+          <t>-0.169070236107786</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>-13.73</t>
+          <t>-0.137299228435607</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>-10.75</t>
+          <t>-0.107493159423523</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>-10.96</t>
+          <t>-0.109581749840273</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>-11.6</t>
+          <t>-0.116025846729601</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>368.71</t>
+          <t>3.68706845021504</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>217.09</t>
+          <t>2.17085170697937</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>232.21</t>
+          <t>2.32209532182875</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>209.93</t>
+          <t>2.09927885149709</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>227.8</t>
+          <t>2.27798965160473</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>242.92</t>
+          <t>2.42915059423324</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>192.97</t>
+          <t>1.92973338330295</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>135.57</t>
+          <t>1.35570790849498</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>97.11</t>
+          <t>0.971130075522464</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>88.72</t>
+          <t>0.887197516057833</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>79.48</t>
+          <t>0.794765370609245</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>67.48</t>
+          <t>0.674788950503795</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>56.68</t>
+          <t>0.56681263777302</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>36.17</t>
+          <t>0.361664334914378</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>49.59</t>
+          <t>0.495893392044067</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-61.1</t>
+          <t>-0.611013918156263</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-59.81</t>
+          <t>-0.59808493590178</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>-55.41</t>
+          <t>-0.554109834737905</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-54.68</t>
+          <t>-0.546804941151093</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-52.07</t>
+          <t>-0.520733930638885</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-47.1</t>
+          <t>-0.470988160958597</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-47.72</t>
+          <t>-0.477154542074688</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-50.29</t>
+          <t>-0.502943956419493</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>-56.3</t>
+          <t>-0.563019854272539</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-56.16</t>
+          <t>-0.561552057200176</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>-54.83</t>
+          <t>-0.548305845503459</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>-54.13</t>
+          <t>-0.541302137537109</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>-53.41</t>
+          <t>-0.534060330913649</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>-53.91</t>
+          <t>-0.539134672240811</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>-54.7</t>
+          <t>-0.546974888894795</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-60.17</t>
+          <t>-0.601676016821963</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-59.7</t>
+          <t>-0.596986607405909</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>-55.1</t>
+          <t>-0.550966027418143</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-55.86</t>
+          <t>-0.558566148158476</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-53.25</t>
+          <t>-0.53250567460812</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-47.52</t>
+          <t>-0.475206471106263</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-48.56</t>
+          <t>-0.485629986341252</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-51.95</t>
+          <t>-0.519508091128954</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>-58.8</t>
+          <t>-0.588010124839681</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-60.16</t>
+          <t>-0.601561186746264</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>-59.15</t>
+          <t>-0.591529451413627</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>-58.49</t>
+          <t>-0.584892014696826</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>-61.79</t>
+          <t>-0.617915505491665</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>-61.59</t>
+          <t>-0.615872918063591</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>-63.35</t>
+          <t>-0.633521500628679</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-50.34</t>
+          <t>-0.503407353257099</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-48.12</t>
+          <t>-0.481211629290372</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>-41.47</t>
+          <t>-0.414724271475866</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-40.51</t>
+          <t>-0.405100445242544</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-35.44</t>
+          <t>-0.354361085287388</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-24.12</t>
+          <t>-0.241195984832408</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-24.94</t>
+          <t>-0.24935932076598</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-29.3</t>
+          <t>-0.293026115890029</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>-39.02</t>
+          <t>-0.390226537337657</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-40.6</t>
+          <t>-0.405960008094677</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>-38.12</t>
+          <t>-0.381183867377623</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>-37.75</t>
+          <t>-0.377526763033722</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>-39.22</t>
+          <t>-0.392200952912184</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>-41.38</t>
+          <t>-0.413812470342084</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>-41.47</t>
+          <t>-0.414732046526756</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>596.73</t>
+          <t>5.96730641556627</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>475.59</t>
+          <t>4.75587649281007</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>435.64</t>
+          <t>4.35635215674345</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>366.92</t>
+          <t>3.66917302488511</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>363.76</t>
+          <t>3.63757233559194</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>365.96</t>
+          <t>3.65963694865974</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>338.49</t>
+          <t>3.38494947256135</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>289.14</t>
+          <t>2.89141077153536</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>202.75</t>
+          <t>2.02746121580317</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>173.28</t>
+          <t>1.73280080497325</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>168.62</t>
+          <t>1.68619667372628</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>142.76</t>
+          <t>1.42762481509001</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>98.81</t>
+          <t>0.988135350494707</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>75.78</t>
+          <t>0.757818267698992</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>75.62</t>
+          <t>0.756171383930428</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-48.53</t>
+          <t>-0.485299274226921</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>-46</t>
+          <t>-0.459991915665712</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>-40.55</t>
+          <t>-0.405498542138859</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-42.22</t>
+          <t>-0.422196020240451</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-38.47</t>
+          <t>-0.384685237865521</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-32.08</t>
+          <t>-0.320828662051026</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-34.25</t>
+          <t>-0.342538913409893</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-37.3</t>
+          <t>-0.373001105542754</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>-45.88</t>
+          <t>-0.458784824834015</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-47.68</t>
+          <t>-0.47681625138187</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>-46.96</t>
+          <t>-0.469623302637252</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>-46.34</t>
+          <t>-0.463366942625404</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>-46.74</t>
+          <t>-0.46735567033869</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>-48.79</t>
+          <t>-0.487863099592166</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>-49.61</t>
+          <t>-0.496073067421391</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-63.16</t>
+          <t>-0.631630385299524</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-61.82</t>
+          <t>-0.61816418653234</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>-57.37</t>
+          <t>-0.573686216957704</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-57.6</t>
+          <t>-0.575968077362235</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-54.17</t>
+          <t>-0.541667562445844</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-49.14</t>
+          <t>-0.49142222567282</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-49.75</t>
+          <t>-0.497496339632317</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-53.94</t>
+          <t>-0.539353341531115</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>-60.68</t>
+          <t>-0.606842822086784</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-61.43</t>
+          <t>-0.614321779359302</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>-60.03</t>
+          <t>-0.600343120012783</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>-59.84</t>
+          <t>-0.598372577087575</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>-59.02</t>
+          <t>-0.590160185361207</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>-59.32</t>
+          <t>-0.59323727546102</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>-58.69</t>
+          <t>-0.586856599773236</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-38.43</t>
+          <t>-0.384265662961186</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>-38.32</t>
+          <t>-0.383163017190386</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>-42.56</t>
+          <t>-0.425593922939893</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-46.12</t>
+          <t>-0.461200042260551</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-44.42</t>
+          <t>-0.444214458965202</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-43.32</t>
+          <t>-0.433227713582641</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-44</t>
+          <t>-0.440036873027938</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-46.85</t>
+          <t>-0.46845898799589</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>-51.21</t>
+          <t>-0.512103986186222</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-54.42</t>
+          <t>-0.544161325838516</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>-53.24</t>
+          <t>-0.532420883242714</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>-53.3</t>
+          <t>-0.533007846963323</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>-53.76</t>
+          <t>-0.537643986565076</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>-47.2</t>
+          <t>-0.47203052741134</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>-40.66</t>
+          <t>-0.406618037822296</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>0.0650093833311285</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>0.0365095934712929</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.0105042913598925</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>0.0556552284434211</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>0.0772116022753251</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>21.64</t>
+          <t>0.216390512429136</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>19.44</t>
+          <t>0.194357651797831</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>0.0531166677539114</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>-12.15</t>
+          <t>-0.121478714463216</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-13.76</t>
+          <t>-0.137629833580085</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>-13.43</t>
+          <t>-0.134326960016999</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>-9.25</t>
+          <t>-0.0925146843088051</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>-13.25</t>
+          <t>-0.132537418738321</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>-17.45</t>
+          <t>-0.174468410402319</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>-23.49</t>
+          <t>-0.234875384012599</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>212.35</t>
+          <t>2.1235069461677</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>215.32</t>
+          <t>2.1531571231706</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>211.7</t>
+          <t>2.1169899058785</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>210.65</t>
+          <t>2.10647524146379</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>249.92</t>
+          <t>2.49923582424842</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>238.41</t>
+          <t>2.38411335547731</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>195.94</t>
+          <t>1.95942288580799</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>140.25</t>
+          <t>1.40248022930218</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>101.25</t>
+          <t>1.01247327898005</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>83.99</t>
+          <t>0.839904078611003</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>79.56</t>
+          <t>0.795629987302004</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>0.893024509071762</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>72.96</t>
+          <t>0.729642602382885</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>0.672951021695052</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>92.54</t>
+          <t>0.925355827256805</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>292.31</t>
+          <t>2.9231208231822</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>279.96</t>
+          <t>2.79963701653857</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>291.41</t>
+          <t>2.91414358823249</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>978.12</t>
+          <t>9.78116252182988</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>764.55</t>
+          <t>7.64547284300299</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>671.48</t>
+          <t>6.71478380219436</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>678.1</t>
+          <t>6.78101491254548</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>579.37</t>
+          <t>5.79372222084372</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>500.52</t>
+          <t>5.00515744854728</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>552.04</t>
+          <t>5.52035343625403</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>446</t>
+          <t>4.46001408374863</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>331.01</t>
+          <t>3.31008081658988</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>309.39</t>
+          <t>3.09391690608097</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>285.94</t>
+          <t>2.85939464404228</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>259.47</t>
+          <t>2.59468707715603</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1832.7</t>
+          <t>18.3269982077914</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1997.5</t>
+          <t>19.9749632646574</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1710.51</t>
+          <t>17.1050805040679</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1693.55</t>
+          <t>16.9355438664786</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1681.8</t>
+          <t>16.8180018856503</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1711.54</t>
+          <t>17.1153614560686</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1699.44</t>
+          <t>16.9944220481114</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1684.94</t>
+          <t>16.8494205637114</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>1643.93</t>
+          <t>16.439302858394</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1569.42</t>
+          <t>15.6941971335656</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>1424.83</t>
+          <t>14.2482938242626</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>1331.31</t>
+          <t>13.3131402257566</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>1184.5</t>
+          <t>11.8450167714403</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>1204.97</t>
+          <t>12.0496532338237</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>1103.27</t>
+          <t>11.0327355929428</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-37.78</t>
+          <t>-0.377818147205161</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-36.92</t>
+          <t>-0.369207364354335</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>-38.56</t>
+          <t>-0.385591831887927</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-37.45</t>
+          <t>-0.374453972539879</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-34.31</t>
+          <t>-0.343143933728933</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-30.45</t>
+          <t>-0.304451389685787</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-34.34</t>
+          <t>-0.343350099326526</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-38.21</t>
+          <t>-0.382136220286067</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>-47.74</t>
+          <t>-0.477410800075412</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-50.27</t>
+          <t>-0.502710522632743</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>-49.94</t>
+          <t>-0.499408614920876</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>-49.78</t>
+          <t>-0.497809925059551</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>-50.87</t>
+          <t>-0.508707037187851</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>-53.75</t>
+          <t>-0.537537402169813</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>-51.73</t>
+          <t>-0.517314446233804</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-61.04</t>
+          <t>-0.610433537778264</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-63.3</t>
+          <t>-0.63304920501551</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>-61.16</t>
+          <t>-0.611574124573115</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-59.02</t>
+          <t>-0.5902379206344</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-55.26</t>
+          <t>-0.552616150984824</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-49.01</t>
+          <t>-0.490082747031913</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-51.25</t>
+          <t>-0.512497024101484</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-53.84</t>
+          <t>-0.538412502081367</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>-59.3</t>
+          <t>-0.592990878552792</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-60.69</t>
+          <t>-0.606896021335956</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>-58.87</t>
+          <t>-0.588692971146657</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>-57.55</t>
+          <t>-0.575517978946796</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>-56.71</t>
+          <t>-0.5671033700267</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>-56.25</t>
+          <t>-0.562546180913718</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>-56.97</t>
+          <t>-0.569727848830966</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>-60.35</t>
+          <t>-0.603476598945362</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>-52.19</t>
+          <t>-0.521917432667577</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>-48.36</t>
+          <t>-0.483618121773505</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-44.23</t>
+          <t>-0.442332657483376</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-48.94</t>
+          <t>-0.489442213243651</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-51.22</t>
+          <t>-0.512226514507224</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>-45.39</t>
+          <t>-0.453933614466351</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>-41.83</t>
+          <t>-0.418261569257293</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>-41.98</t>
+          <t>-0.419835000968224</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-41.3</t>
+          <t>-0.413010909355426</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>-38.1</t>
+          <t>-0.381042216280413</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>-31.5</t>
+          <t>-0.315008140041871</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>-23.63</t>
+          <t>-0.236296964305679</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>-27.69</t>
+          <t>-0.276865354730362</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>-37.17</t>
+          <t>-0.371666670032418</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>47.77</t>
+          <t>0.477710259736975</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>0.403433081581822</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>54.42</t>
+          <t>0.544189432163851</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>127.65</t>
+          <t>1.27652969562649</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>103.67</t>
+          <t>1.03671857695759</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>84.14</t>
+          <t>0.841379229306366</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>94.74</t>
+          <t>0.947380443775563</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>86.08</t>
+          <t>0.860777738565948</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>73.91</t>
+          <t>0.739092244408132</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>82.65</t>
+          <t>0.82651279611249</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>59.73</t>
+          <t>0.597254983951595</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>49.71</t>
+          <t>0.497073651275147</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>50.23</t>
+          <t>0.502252282182164</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>79.06</t>
+          <t>0.790649040129138</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>92.79</t>
+          <t>0.927851698124571</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>903.63</t>
+          <t>9.03629094775529</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>667.87</t>
+          <t>6.67867146201327</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>507.89</t>
+          <t>5.07886583934794</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>414.78</t>
+          <t>4.14783077629748</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>415.79</t>
+          <t>4.15792388237243</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>458.11</t>
+          <t>4.58108796342612</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>408.97</t>
+          <t>4.08965266350539</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>346.81</t>
+          <t>3.4681473174744</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>261.56</t>
+          <t>2.61560680227513</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>230.77</t>
+          <t>2.30774077213938</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>224.89</t>
+          <t>2.24885982191789</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>187.49</t>
+          <t>1.87485426611691</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>161.3</t>
+          <t>1.61302037218244</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>134.1</t>
+          <t>1.3409725540921</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>165.72</t>
+          <t>1.6571507787027</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>-71.75</t>
+          <t>-0.717461279346719</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>-70.65</t>
+          <t>-0.706467363206555</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>-66.61</t>
+          <t>-0.666081266850444</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-65.88</t>
+          <t>-0.658761818037019</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-62.84</t>
+          <t>-0.62840411545479</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-59.58</t>
+          <t>-0.595801826788205</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>-61.19</t>
+          <t>-0.611938164078563</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>-63.83</t>
+          <t>-0.638303099431711</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>-71.48</t>
+          <t>-0.714811853064122</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-67.38</t>
+          <t>-0.673784436237766</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>-66.4</t>
+          <t>-0.663990123309922</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>-67.27</t>
+          <t>-0.672721704803988</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>-66.62</t>
+          <t>-0.666178637149958</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>-68.88</t>
+          <t>-0.688752180557025</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>-66.44</t>
+          <t>-0.664421644195374</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>613.48</t>
+          <t>6.13477022537446</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>502.33</t>
+          <t>5.02333110527934</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>443.7</t>
+          <t>4.43698792856093</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>416.53</t>
+          <t>4.1653448209736</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>397.27</t>
+          <t>3.97274430301344</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>385.1</t>
+          <t>3.85095481289536</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>357.41</t>
+          <t>3.57414125038716</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>332.94</t>
+          <t>3.32941242456067</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>264.99</t>
+          <t>2.64988855107075</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>240.78</t>
+          <t>2.4077547287667</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>198.1</t>
+          <t>1.98102290504386</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>148.8</t>
+          <t>1.48803831521725</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>89.82</t>
+          <t>0.89815945877857</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>63.02</t>
+          <t>0.630245848257664</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>92.58</t>
+          <t>0.92578655299026</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>263.26</t>
+          <t>2.63255136882003</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>260.02</t>
+          <t>2.60015028084696</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>203.99</t>
+          <t>2.03994237733378</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>180.13</t>
+          <t>1.80134766941118</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>159.5</t>
+          <t>1.5949591668413</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>120.22</t>
+          <t>1.2021553290139</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>100.1</t>
+          <t>1.00096869943769</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>99.52</t>
+          <t>0.995171548348951</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>127.3</t>
+          <t>1.27301280143528</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>154.58</t>
+          <t>1.54583228696719</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>150.81</t>
+          <t>1.50805689351178</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>147.96</t>
+          <t>1.47960437142384</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>164.2</t>
+          <t>1.64202292514359</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>190.37</t>
+          <t>1.90374260863309</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>236.08</t>
+          <t>2.36077844929562</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>-11.76</t>
+          <t>-0.117601198538701</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>-14.5</t>
+          <t>-0.144954385510027</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>-16.26</t>
+          <t>-0.162645922045133</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-23.88</t>
+          <t>-0.238816290468603</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-20.97</t>
+          <t>-0.209665892554193</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-17.25</t>
+          <t>-0.17252015605038</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>-33.07</t>
+          <t>-0.330731199166461</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>-25.88</t>
+          <t>-0.258773624341776</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>-31.81</t>
+          <t>-0.318100025984723</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-30.46</t>
+          <t>-0.304637565028544</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>-27.31</t>
+          <t>-0.273054625996913</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>-25.94</t>
+          <t>-0.259399755119709</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>-23.75</t>
+          <t>-0.237468447396964</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>-31.43</t>
+          <t>-0.314259040460635</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>-29.33</t>
+          <t>-0.293290281113408</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>-61.86</t>
+          <t>-0.618561509035186</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-59.11</t>
+          <t>-0.591075085701249</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>-53.77</t>
+          <t>-0.537747196372216</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-55.32</t>
+          <t>-0.553178361466145</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-50.93</t>
+          <t>-0.509267790032172</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-50.33</t>
+          <t>-0.503347145123723</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-52.81</t>
+          <t>-0.528120861328625</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-55.33</t>
+          <t>-0.553296122004625</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>-60.49</t>
+          <t>-0.604859437553278</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-61.21</t>
+          <t>-0.612078757873827</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>-59.32</t>
+          <t>-0.593154923543323</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>-58.75</t>
+          <t>-0.587536534607838</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>-58.94</t>
+          <t>-0.589407204575395</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>-60.14</t>
+          <t>-0.601359638499493</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>-60.71</t>
+          <t>-0.607139184852795</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>181.2</t>
+          <t>1.81204084607569</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>145.14</t>
+          <t>1.45140286978415</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>138.68</t>
+          <t>1.38683210010846</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>116.31</t>
+          <t>1.1631251854619</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>1.40499830025403</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>149.42</t>
+          <t>1.49415871588438</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>133.63</t>
+          <t>1.33625162630217</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>1.34502061654701</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>137.59</t>
+          <t>1.37585650414766</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>144.78</t>
+          <t>1.4478375107834</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>126.07</t>
+          <t>1.26074110393519</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>124.63</t>
+          <t>1.24629606359057</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>111.98</t>
+          <t>1.11984696385563</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>80.62</t>
+          <t>0.806223998065675</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>119.47</t>
+          <t>1.19469864746446</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>-32.5</t>
+          <t>-0.325013042241723</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>-34.12</t>
+          <t>-0.341235561621565</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>-34.64</t>
+          <t>-0.346433136854004</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-40.86</t>
+          <t>-0.40861489260427</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-37.86</t>
+          <t>-0.378643348063977</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-33.25</t>
+          <t>-0.332457280563238</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>-35</t>
+          <t>-0.34998829992532</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>-38.77</t>
+          <t>-0.387684903137683</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>-44.23</t>
+          <t>-0.442273925490204</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-43.89</t>
+          <t>-0.438887642743554</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>-42.24</t>
+          <t>-0.422413167125913</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>-38.08</t>
+          <t>-0.380842454518255</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>-36.77</t>
+          <t>-0.367695693094844</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>-36.21</t>
+          <t>-0.362075713099918</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>-34.94</t>
+          <t>-0.349367169278537</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>319.76</t>
+          <t>3.19755903997404</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>341.21</t>
+          <t>3.41213220976834</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>367.76</t>
+          <t>3.67758411360776</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>212.76</t>
+          <t>2.12760572203113</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>369.34</t>
+          <t>3.69342293211957</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>292.79</t>
+          <t>2.92792706163262</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>237.36</t>
+          <t>2.37364682911371</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>242.91</t>
+          <t>2.42907426580303</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>212.09</t>
+          <t>2.12094901169103</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>194.61</t>
+          <t>1.94613240261553</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>123.55</t>
+          <t>1.23550174545334</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>103.78</t>
+          <t>1.03784272335276</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>65.19</t>
+          <t>0.651850965122847</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>0.442954428727979</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>84.93</t>
+          <t>0.849284433674738</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>689.28</t>
+          <t>6.89281100677284</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>543.54</t>
+          <t>5.43542218679376</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>522.92</t>
+          <t>5.22921463960077</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>677.06</t>
+          <t>6.77055709179668</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1302.47</t>
+          <t>13.024749928656</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>982.34</t>
+          <t>9.82339386858012</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>799.52</t>
+          <t>7.99523470073347</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>680.48</t>
+          <t>6.80478968307779</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>573.62</t>
+          <t>5.7361947744024</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>461.69</t>
+          <t>4.61693398354901</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>379.33</t>
+          <t>3.7932537711522</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>289.98</t>
+          <t>2.89984328894402</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>228.66</t>
+          <t>2.28664080076017</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>156.99</t>
+          <t>1.56985475485703</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>215.59</t>
+          <t>2.15591366190698</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>513.49</t>
+          <t>5.13490480499409</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>450.76</t>
+          <t>4.50755331369438</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>401.01</t>
+          <t>4.01007823109722</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>370.27</t>
+          <t>3.7026944177882</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>438.02</t>
+          <t>4.38018458699245</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>424.12</t>
+          <t>4.24121301938437</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>408.23</t>
+          <t>4.08232848384873</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>337.14</t>
+          <t>3.37144283646852</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>232.82</t>
+          <t>2.32821817302115</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>203.34</t>
+          <t>2.03336503141739</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>190.21</t>
+          <t>1.90208715664801</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>166.37</t>
+          <t>1.66369665944284</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>129.62</t>
+          <t>1.29620695196191</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>96.68</t>
+          <t>0.966843436229248</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>82.49</t>
+          <t>0.824922994777093</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>12.31</t>
+          <t>0.123070733222525</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>14.85</t>
+          <t>0.14846815924163</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>17.07</t>
+          <t>0.170728336802614</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>12.12</t>
+          <t>0.121175841932453</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>19.24</t>
+          <t>0.192410795927278</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>32.52</t>
+          <t>0.325213351751695</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>21.44</t>
+          <t>0.214354085537412</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>14.57</t>
+          <t>0.145741677507871</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.00118331930183779</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>-0.0448286790123957</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-0.033077975257339</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-0.0281261605944694</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>-6.59</t>
+          <t>-0.0658880427266285</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>-12.04</t>
+          <t>-0.120427821412582</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>-11.57</t>
+          <t>-0.115685162103066</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>-53.52</t>
+          <t>-0.535243002369054</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>-58.07</t>
+          <t>-0.580664734813894</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>-54.84</t>
+          <t>-0.54836090332962</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-54.38</t>
+          <t>-0.543812416293402</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-50.66</t>
+          <t>-0.506614672935376</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-47.21</t>
+          <t>-0.472132725170136</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>-44.08</t>
+          <t>-0.440782559620945</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>-48.52</t>
+          <t>-0.485232930703132</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>-56.65</t>
+          <t>-0.56654845733987</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-57.57</t>
+          <t>-0.575666524253355</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>-55.67</t>
+          <t>-0.55674908789131</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>-54.46</t>
+          <t>-0.544617152508383</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>-54.95</t>
+          <t>-0.549474441609131</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>-52.86</t>
+          <t>-0.528648975570256</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>-48.19</t>
+          <t>-0.48192961160884</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>176.66</t>
+          <t>1.76661753677784</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>152.89</t>
+          <t>1.52894046869495</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>123.22</t>
+          <t>1.23216022645466</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>110.93</t>
+          <t>1.10926240066229</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>91.05</t>
+          <t>0.910516564474192</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>102.19</t>
+          <t>1.02186816206769</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>169.21</t>
+          <t>1.69211166470296</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>190.96</t>
+          <t>1.9096435163196</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>150.83</t>
+          <t>1.50833884660388</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>105.75</t>
+          <t>1.05750732839555</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>90.38</t>
+          <t>0.903783150154902</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>87.92</t>
+          <t>0.879232486105836</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>74.39</t>
+          <t>0.743939820696563</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>72.86</t>
+          <t>0.728643099479101</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>100.33</t>
+          <t>1.00326289576165</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>-5.74</t>
+          <t>-0.0573524190848314</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>-7.3</t>
+          <t>-0.0730369310509388</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>-7.6</t>
+          <t>-0.0759682140611631</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>0.0348520749381676</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>0.0327692915059428</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.00855768038242399</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>0.0235921341920637</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>0.0992383644072476</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>16.56</t>
+          <t>0.16564527345053</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>24.66</t>
+          <t>0.246574590623898</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>25.67</t>
+          <t>0.256727471684836</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>31.96</t>
+          <t>0.319576618874752</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>50.07</t>
+          <t>0.50068528758494</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>62.65</t>
+          <t>0.626504546494268</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>0.71196245753075</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>-38.29</t>
+          <t>-0.38292889506702</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>-39.12</t>
+          <t>-0.391153015027818</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>-42.2</t>
+          <t>-0.421959201162034</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-44.48</t>
+          <t>-0.44479239132267</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-44.59</t>
+          <t>-0.445944585076676</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-47.73</t>
+          <t>-0.477270665138493</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>-51.35</t>
+          <t>-0.513517147912586</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>-52.34</t>
+          <t>-0.523357839231331</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>-52.23</t>
+          <t>-0.522315483564734</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-49.48</t>
+          <t>-0.494825815531717</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>-48.8</t>
+          <t>-0.487974053979605</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>-48.08</t>
+          <t>-0.480756136333693</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>-44.43</t>
+          <t>-0.444256290956941</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>-41.58</t>
+          <t>-0.415847712959082</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>-44.67</t>
+          <t>-0.446686985401967</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>194.14</t>
+          <t>1.94143167477779</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>195.31</t>
+          <t>1.9530644364802</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>194.88</t>
+          <t>1.94884917163846</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>202.75</t>
+          <t>2.02745718192525</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>214.23</t>
+          <t>2.1423083703878</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>212.75</t>
+          <t>2.12746752098331</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>224.08</t>
+          <t>2.24076165802043</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>245.55</t>
+          <t>2.45545601923489</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>253.35</t>
+          <t>2.53346450003301</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>258.5</t>
+          <t>2.58498435093673</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>240.21</t>
+          <t>2.40210453313808</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>227.95</t>
+          <t>2.27950361785805</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>232.95</t>
+          <t>2.32948547375827</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>214.89</t>
+          <t>2.14887283315033</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>233.56</t>
+          <t>2.33556065189688</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>25.14</t>
+          <t>0.251394415402656</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>29.22</t>
+          <t>0.29222258083501</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>30.91</t>
+          <t>0.309140744509998</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>30.57</t>
+          <t>0.305653634645757</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>33.13</t>
+          <t>0.331329906864738</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>32.42</t>
+          <t>0.324170938042623</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>34.57</t>
+          <t>0.345714899078112</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>35.99</t>
+          <t>0.359874894787074</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>34.81</t>
+          <t>0.348072272098422</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>37.78</t>
+          <t>0.377836726065842</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>38.84</t>
+          <t>0.38836616187349</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>39.21</t>
+          <t>0.392106378663825</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>43.54</t>
+          <t>0.435388875472064</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>0.454961778492714</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>47.13</t>
+          <t>0.47131827673284</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Petrovic</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpPE</t>
